--- a/data/sources/countries/jamaica.xlsx
+++ b/data/sources/countries/jamaica.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,23 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,9 +48,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,377 +414,293 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI122"/>
+  <dimension ref="A1:BE122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="70" customWidth="1" min="16" max="16"/>
-    <col width="70" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="14" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="14" customWidth="1" min="39" max="39"/>
-    <col width="14" customWidth="1" min="40" max="40"/>
-    <col width="14" customWidth="1" min="41" max="41"/>
-    <col width="14" customWidth="1" min="42" max="42"/>
-    <col width="14" customWidth="1" min="43" max="43"/>
-    <col width="14" customWidth="1" min="44" max="44"/>
-    <col width="14" customWidth="1" min="45" max="45"/>
-    <col width="14" customWidth="1" min="46" max="46"/>
-    <col width="14" customWidth="1" min="47" max="47"/>
-    <col width="14" customWidth="1" min="48" max="48"/>
-    <col width="14" customWidth="1" min="49" max="49"/>
-    <col width="14" customWidth="1" min="50" max="50"/>
-    <col width="14" customWidth="1" min="51" max="51"/>
-    <col width="14" customWidth="1" min="52" max="52"/>
-    <col width="14" customWidth="1" min="53" max="53"/>
-    <col width="14" customWidth="1" min="54" max="54"/>
-    <col width="80" customWidth="1" min="55" max="55"/>
-    <col width="14" customWidth="1" min="56" max="56"/>
-    <col width="26" customWidth="1" min="57" max="57"/>
-    <col width="14" customWidth="1" min="58" max="58"/>
-    <col width="14" customWidth="1" min="59" max="59"/>
-    <col width="14" customWidth="1" min="60" max="60"/>
-    <col width="14" customWidth="1" min="61" max="61"/>
-    <col width="14" customWidth="1" min="62" max="62"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Id_Investment</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Id_Investment_Original</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Id_Seq</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Coordinates</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_ALPHA3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_NUM</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Province_ISO</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Investor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Vector</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Path</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Area_EN</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Area_ES</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Detail_ES</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Detail_EN</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Investment</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Joint_Venture</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Origin_Of_Seller</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Stake</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Project_Type</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>News</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Caso1</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Link1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Caso2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Link2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Caso3</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Link3</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Caso4</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Link4</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Caso5</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Link5</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Caso6</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Link6</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Caso7</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Link7</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Caso8</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Link8</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Caso9</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Link9</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Caso10</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Link10</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Caso11</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Link11</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Caso12</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Link12</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Caso13</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>Link13</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>Caso14</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Link14</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>reliability_score</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>reliability_notes</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>cancelled</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>cancelled_motivo</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source1</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>source2</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>source3</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>source4</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>source5</t>
         </is>
       </c>
     </row>
@@ -824,7 +728,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -896,20 +800,20 @@
       <c r="BA2" t="n">
         <v>5</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BB2" t="n">
         <v>0</v>
       </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE2" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -939,7 +843,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -1011,20 +915,20 @@
       <c r="BA3" t="n">
         <v>5</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BB3" t="n">
         <v>0</v>
       </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE3" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -1054,7 +958,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -1126,20 +1030,20 @@
       <c r="BA4" t="n">
         <v>5</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BB4" t="n">
         <v>0</v>
       </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE4" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -1169,7 +1073,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -1241,20 +1145,20 @@
       <c r="BA5" t="n">
         <v>5</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BB5" t="n">
         <v>0</v>
       </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE5" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -1284,7 +1188,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -1356,20 +1260,20 @@
       <c r="BA6" t="n">
         <v>5</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BB6" t="n">
         <v>0</v>
       </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE6" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -1399,7 +1303,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -1471,20 +1375,20 @@
       <c r="BA7" t="n">
         <v>5</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BB7" t="n">
         <v>0</v>
       </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE7" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -1514,7 +1418,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -1586,20 +1490,20 @@
       <c r="BA8" t="n">
         <v>5</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BB8" t="n">
         <v>0</v>
       </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE8" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -1629,7 +1533,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -1701,20 +1605,20 @@
       <c r="BA9" t="n">
         <v>5</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BB9" t="n">
         <v>0</v>
       </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE9" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -1744,7 +1648,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -1816,20 +1720,20 @@
       <c r="BA10" t="n">
         <v>5</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BB10" t="n">
         <v>0</v>
       </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE10" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -1859,7 +1763,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -1931,20 +1835,20 @@
       <c r="BA11" t="n">
         <v>5</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BB11" t="n">
         <v>0</v>
       </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE11" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -1974,7 +1878,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -2046,20 +1950,20 @@
       <c r="BA12" t="n">
         <v>5</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BB12" t="n">
         <v>0</v>
       </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE12" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -2089,7 +1993,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -2161,20 +2065,20 @@
       <c r="BA13" t="n">
         <v>5</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BB13" t="n">
         <v>0</v>
       </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE13" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -2204,7 +2108,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -2276,20 +2180,20 @@
       <c r="BA14" t="n">
         <v>5</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BB14" t="n">
         <v>0</v>
       </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE14" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -2319,7 +2223,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -2391,20 +2295,20 @@
       <c r="BA15" t="n">
         <v>5</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BB15" t="n">
         <v>0</v>
       </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE15" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -2434,7 +2338,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -2506,20 +2410,20 @@
       <c r="BA16" t="n">
         <v>5</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BB16" t="n">
         <v>0</v>
       </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE16" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -2549,7 +2453,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -2621,20 +2525,20 @@
       <c r="BA17" t="n">
         <v>5</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BB17" t="n">
         <v>0</v>
       </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE17" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -2664,7 +2568,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -2736,20 +2640,20 @@
       <c r="BA18" t="n">
         <v>5</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BB18" t="n">
         <v>0</v>
       </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE18" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -2779,7 +2683,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -2851,20 +2755,20 @@
       <c r="BA19" t="n">
         <v>5</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BB19" t="n">
         <v>0</v>
       </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE19" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -2894,7 +2798,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -2966,20 +2870,20 @@
       <c r="BA20" t="n">
         <v>5</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BB20" t="n">
         <v>0</v>
       </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE20" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -3009,7 +2913,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -3081,20 +2985,20 @@
       <c r="BA21" t="n">
         <v>5</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BB21" t="n">
         <v>0</v>
       </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE21" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -3124,7 +3028,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -3196,20 +3100,20 @@
       <c r="BA22" t="n">
         <v>5</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BB22" t="n">
         <v>0</v>
       </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE22" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -3239,7 +3143,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -3311,20 +3215,20 @@
       <c r="BA23" t="n">
         <v>5</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BB23" t="n">
         <v>0</v>
       </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE23" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF23" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -3354,7 +3258,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -3426,20 +3330,20 @@
       <c r="BA24" t="n">
         <v>5</v>
       </c>
-      <c r="BC24" t="n">
+      <c r="BB24" t="n">
         <v>0</v>
       </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE24" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF24" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG24" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -3469,7 +3373,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -3541,20 +3445,20 @@
       <c r="BA25" t="n">
         <v>5</v>
       </c>
-      <c r="BC25" t="n">
+      <c r="BB25" t="n">
         <v>0</v>
       </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE25" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF25" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG25" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -3584,7 +3488,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -3656,20 +3560,20 @@
       <c r="BA26" t="n">
         <v>5</v>
       </c>
-      <c r="BC26" t="n">
+      <c r="BB26" t="n">
         <v>0</v>
       </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE26" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF26" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG26" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -3699,7 +3603,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -3771,20 +3675,20 @@
       <c r="BA27" t="n">
         <v>5</v>
       </c>
-      <c r="BC27" t="n">
+      <c r="BB27" t="n">
         <v>0</v>
       </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE27" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF27" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG27" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -3814,7 +3718,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -3886,20 +3790,20 @@
       <c r="BA28" t="n">
         <v>5</v>
       </c>
-      <c r="BC28" t="n">
+      <c r="BB28" t="n">
         <v>0</v>
       </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE28" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF28" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG28" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -3929,7 +3833,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -4001,20 +3905,20 @@
       <c r="BA29" t="n">
         <v>5</v>
       </c>
-      <c r="BC29" t="n">
+      <c r="BB29" t="n">
         <v>0</v>
       </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE29" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF29" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG29" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -4044,7 +3948,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -4116,20 +4020,20 @@
       <c r="BA30" t="n">
         <v>5</v>
       </c>
-      <c r="BC30" t="n">
+      <c r="BB30" t="n">
         <v>0</v>
       </c>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE30" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF30" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG30" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -4159,7 +4063,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -4231,20 +4135,20 @@
       <c r="BA31" t="n">
         <v>5</v>
       </c>
-      <c r="BC31" t="n">
+      <c r="BB31" t="n">
         <v>0</v>
       </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE31" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF31" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG31" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -4274,7 +4178,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -4346,20 +4250,20 @@
       <c r="BA32" t="n">
         <v>5</v>
       </c>
-      <c r="BC32" t="n">
+      <c r="BB32" t="n">
         <v>0</v>
       </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE32" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF32" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG32" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -4389,7 +4293,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -4461,20 +4365,20 @@
       <c r="BA33" t="n">
         <v>5</v>
       </c>
-      <c r="BC33" t="n">
+      <c r="BB33" t="n">
         <v>0</v>
       </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE33" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF33" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG33" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -4504,7 +4408,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -4576,20 +4480,20 @@
       <c r="BA34" t="n">
         <v>5</v>
       </c>
-      <c r="BC34" t="n">
+      <c r="BB34" t="n">
         <v>0</v>
       </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE34" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF34" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -4619,7 +4523,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -4691,20 +4595,20 @@
       <c r="BA35" t="n">
         <v>5</v>
       </c>
-      <c r="BC35" t="n">
+      <c r="BB35" t="n">
         <v>0</v>
       </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE35" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF35" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG35" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -4734,7 +4638,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -4806,20 +4710,20 @@
       <c r="BA36" t="n">
         <v>5</v>
       </c>
-      <c r="BC36" t="n">
+      <c r="BB36" t="n">
         <v>0</v>
       </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE36" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF36" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG36" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -4849,7 +4753,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -4921,20 +4825,20 @@
       <c r="BA37" t="n">
         <v>5</v>
       </c>
-      <c r="BC37" t="n">
+      <c r="BB37" t="n">
         <v>0</v>
       </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE37" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF37" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG37" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -4964,7 +4868,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -5036,20 +4940,20 @@
       <c r="BA38" t="n">
         <v>5</v>
       </c>
-      <c r="BC38" t="n">
+      <c r="BB38" t="n">
         <v>0</v>
       </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE38" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF38" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG38" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -5079,7 +4983,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -5151,20 +5055,20 @@
       <c r="BA39" t="n">
         <v>5</v>
       </c>
-      <c r="BC39" t="n">
+      <c r="BB39" t="n">
         <v>0</v>
       </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE39" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF39" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG39" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -5194,7 +5098,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -5266,20 +5170,20 @@
       <c r="BA40" t="n">
         <v>5</v>
       </c>
-      <c r="BC40" t="n">
+      <c r="BB40" t="n">
         <v>0</v>
       </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE40" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF40" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG40" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -5309,7 +5213,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -5381,20 +5285,20 @@
       <c r="BA41" t="n">
         <v>5</v>
       </c>
-      <c r="BC41" t="n">
+      <c r="BB41" t="n">
         <v>0</v>
       </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE41" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF41" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG41" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -5424,7 +5328,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -5496,20 +5400,20 @@
       <c r="BA42" t="n">
         <v>5</v>
       </c>
-      <c r="BC42" t="n">
+      <c r="BB42" t="n">
         <v>0</v>
       </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE42" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF42" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG42" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -5539,7 +5443,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -5611,20 +5515,20 @@
       <c r="BA43" t="n">
         <v>5</v>
       </c>
-      <c r="BC43" t="n">
+      <c r="BB43" t="n">
         <v>0</v>
       </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE43" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF43" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG43" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -5654,7 +5558,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -5726,20 +5630,20 @@
       <c r="BA44" t="n">
         <v>5</v>
       </c>
-      <c r="BC44" t="n">
+      <c r="BB44" t="n">
         <v>0</v>
       </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE44" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF44" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG44" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -5769,7 +5673,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -5841,20 +5745,20 @@
       <c r="BA45" t="n">
         <v>5</v>
       </c>
-      <c r="BC45" t="n">
+      <c r="BB45" t="n">
         <v>0</v>
       </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE45" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF45" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG45" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -5884,7 +5788,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -5956,20 +5860,20 @@
       <c r="BA46" t="n">
         <v>5</v>
       </c>
-      <c r="BC46" t="n">
+      <c r="BB46" t="n">
         <v>0</v>
       </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE46" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF46" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG46" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -5999,7 +5903,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -6071,20 +5975,20 @@
       <c r="BA47" t="n">
         <v>5</v>
       </c>
-      <c r="BC47" t="n">
+      <c r="BB47" t="n">
         <v>0</v>
       </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE47" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF47" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG47" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -6114,7 +6018,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -6186,20 +6090,20 @@
       <c r="BA48" t="n">
         <v>5</v>
       </c>
-      <c r="BC48" t="n">
+      <c r="BB48" t="n">
         <v>0</v>
       </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE48" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF48" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG48" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -6229,7 +6133,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -6301,20 +6205,20 @@
       <c r="BA49" t="n">
         <v>5</v>
       </c>
-      <c r="BC49" t="n">
+      <c r="BB49" t="n">
         <v>0</v>
       </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE49" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF49" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG49" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -6344,7 +6248,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -6416,20 +6320,20 @@
       <c r="BA50" t="n">
         <v>5</v>
       </c>
-      <c r="BC50" t="n">
+      <c r="BB50" t="n">
         <v>0</v>
       </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE50" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF50" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG50" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -6459,7 +6363,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -6531,20 +6435,20 @@
       <c r="BA51" t="n">
         <v>5</v>
       </c>
-      <c r="BC51" t="n">
+      <c r="BB51" t="n">
         <v>0</v>
       </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE51" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF51" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG51" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -6574,7 +6478,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -6646,20 +6550,20 @@
       <c r="BA52" t="n">
         <v>5</v>
       </c>
-      <c r="BC52" t="n">
+      <c r="BB52" t="n">
         <v>0</v>
       </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE52" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF52" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG52" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -6689,7 +6593,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -6761,20 +6665,20 @@
       <c r="BA53" t="n">
         <v>5</v>
       </c>
-      <c r="BC53" t="n">
+      <c r="BB53" t="n">
         <v>0</v>
       </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE53" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF53" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG53" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -6804,7 +6708,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -6876,20 +6780,20 @@
       <c r="BA54" t="n">
         <v>5</v>
       </c>
-      <c r="BC54" t="n">
+      <c r="BB54" t="n">
         <v>0</v>
       </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE54" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF54" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG54" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -6919,7 +6823,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -6991,20 +6895,20 @@
       <c r="BA55" t="n">
         <v>5</v>
       </c>
-      <c r="BC55" t="n">
+      <c r="BB55" t="n">
         <v>0</v>
       </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE55" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF55" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG55" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -7034,7 +6938,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -7106,20 +7010,20 @@
       <c r="BA56" t="n">
         <v>5</v>
       </c>
-      <c r="BC56" t="n">
+      <c r="BB56" t="n">
         <v>0</v>
       </c>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
+        </is>
+      </c>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
+        </is>
+      </c>
       <c r="BE56" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/implementation-and-concession-agreements-signed-for-northsouth-link-of-highway-2000/</t>
-        </is>
-      </c>
-      <c r="BF56" t="inlineStr">
-        <is>
-          <t>http://past.jamaica-gleaner.com/article/business/20160601/chinese-development-financing-jamaica-surpasses-100b</t>
-        </is>
-      </c>
-      <c r="BG56" t="inlineStr">
         <is>
           <t>https://jnshc.com/page/corporate-profile</t>
         </is>
@@ -7149,7 +7053,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -7164,7 +7068,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Jiuquan Iron &amp; Steel</t>
+          <t>Jiuquan Iron &amp; Steel Group (JISCO)</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -7229,20 +7133,20 @@
       <c r="BA57" t="n">
         <v>4</v>
       </c>
-      <c r="BC57" t="n">
+      <c r="BB57" t="n">
         <v>0</v>
       </c>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>https://www.moa.gov.jm/content/jisco-commits-us490-million-first-phase-investment-towards-reopening-alpart</t>
+        </is>
+      </c>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>https://thepeoplesmap.net/country/jamaica/</t>
+        </is>
+      </c>
       <c r="BE57" t="inlineStr">
-        <is>
-          <t>https://www.moa.gov.jm/content/jisco-commits-us490-million-first-phase-investment-towards-reopening-alpart</t>
-        </is>
-      </c>
-      <c r="BF57" t="inlineStr">
-        <is>
-          <t>https://thepeoplesmap.net/country/jamaica/</t>
-        </is>
-      </c>
-      <c r="BG57" t="inlineStr">
         <is>
           <t>https://jamaica-gleaner.com/article/commentary/20190926/editorial-what-future-chinese-investment-jamaica</t>
         </is>
@@ -7272,7 +7176,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G58" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -7287,7 +7191,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Jiuquan Iron &amp; Steel</t>
+          <t>Jiuquan Iron &amp; Steel Group (JISCO)</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -7344,20 +7248,20 @@
       <c r="BA58" t="n">
         <v>4</v>
       </c>
-      <c r="BC58" t="n">
+      <c r="BB58" t="n">
         <v>0</v>
       </c>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>https://www.moa.gov.jm/content/jisco-commits-us490-million-first-phase-investment-towards-reopening-alpart</t>
+        </is>
+      </c>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>https://jamaica-gleaner.com/article/news/20260707/jisco-commits-us490-million-first-phase-investment-towards-reopening-alpart</t>
+        </is>
+      </c>
       <c r="BE58" t="inlineStr">
-        <is>
-          <t>https://www.moa.gov.jm/content/jisco-commits-us490-million-first-phase-investment-towards-reopening-alpart</t>
-        </is>
-      </c>
-      <c r="BF58" t="inlineStr">
-        <is>
-          <t>https://jamaica-gleaner.com/article/news/20260707/jisco-commits-us490-million-first-phase-investment-towards-reopening-alpart</t>
-        </is>
-      </c>
-      <c r="BG58" t="inlineStr">
         <is>
           <t>https://www.jamaicaobserver.com/2026/07/08/alpart-resume-operations-june-2027/</t>
         </is>
@@ -7387,7 +7291,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G59" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -7402,7 +7306,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>COMPLANT</t>
+          <t>COMPLANT International Sugar Industry Co.</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -7467,20 +7371,20 @@
       <c r="BA59" t="n">
         <v>4</v>
       </c>
-      <c r="BC59" t="n">
+      <c r="BB59" t="n">
         <v>0</v>
       </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/government/agencies/sugar-company-jamaica-scj-legacy/</t>
+        </is>
+      </c>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>https://jamaica-gleaner.com/article/business/20191101/failed-decade-sugar-privatisation</t>
+        </is>
+      </c>
       <c r="BE59" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/government/agencies/sugar-company-jamaica-scj-legacy/</t>
-        </is>
-      </c>
-      <c r="BF59" t="inlineStr">
-        <is>
-          <t>https://jamaica-gleaner.com/article/business/20191101/failed-decade-sugar-privatisation</t>
-        </is>
-      </c>
-      <c r="BG59" t="inlineStr">
         <is>
           <t>https://radiojamaicanewsonline.com/business/pan-caribbean-sugar-company-invests-us160-million-in-sugar-industry</t>
         </is>
@@ -7510,7 +7414,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -7525,7 +7429,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>COMPLANT</t>
+          <t>COMPLANT International Sugar Industry Co.</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -7590,20 +7494,20 @@
       <c r="BA60" t="n">
         <v>4</v>
       </c>
-      <c r="BC60" t="n">
+      <c r="BB60" t="n">
         <v>0</v>
       </c>
+      <c r="BC60" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/government/agencies/sugar-company-jamaica-scj-legacy/</t>
+        </is>
+      </c>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>https://jamaica-gleaner.com/article/business/20191101/failed-decade-sugar-privatisation</t>
+        </is>
+      </c>
       <c r="BE60" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/government/agencies/sugar-company-jamaica-scj-legacy/</t>
-        </is>
-      </c>
-      <c r="BF60" t="inlineStr">
-        <is>
-          <t>https://jamaica-gleaner.com/article/business/20191101/failed-decade-sugar-privatisation</t>
-        </is>
-      </c>
-      <c r="BG60" t="inlineStr">
         <is>
           <t>https://radiojamaicanewsonline.com/business/pan-caribbean-sugar-company-invests-us160-million-in-sugar-industry</t>
         </is>
@@ -7633,7 +7537,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -7648,7 +7552,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>COMPLANT</t>
+          <t>COMPLANT International Sugar Industry Co.</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -7713,20 +7617,20 @@
       <c r="BA61" t="n">
         <v>4</v>
       </c>
-      <c r="BC61" t="n">
+      <c r="BB61" t="n">
         <v>0</v>
       </c>
+      <c r="BC61" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/government/agencies/sugar-company-jamaica-scj-legacy/</t>
+        </is>
+      </c>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>https://jamaica-gleaner.com/article/business/20191101/failed-decade-sugar-privatisation</t>
+        </is>
+      </c>
       <c r="BE61" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/government/agencies/sugar-company-jamaica-scj-legacy/</t>
-        </is>
-      </c>
-      <c r="BF61" t="inlineStr">
-        <is>
-          <t>https://jamaica-gleaner.com/article/business/20191101/failed-decade-sugar-privatisation</t>
-        </is>
-      </c>
-      <c r="BG61" t="inlineStr">
         <is>
           <t>https://radiojamaicanewsonline.com/business/pan-caribbean-sugar-company-invests-us160-million-in-sugar-industry</t>
         </is>
@@ -7756,7 +7660,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -7771,7 +7675,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -7828,20 +7732,20 @@
       <c r="BA62" t="n">
         <v>5</v>
       </c>
-      <c r="BC62" t="n">
+      <c r="BB62" t="n">
         <v>0</v>
       </c>
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE62" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF62" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG62" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -7871,7 +7775,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G63" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -7886,7 +7790,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -7943,20 +7847,20 @@
       <c r="BA63" t="n">
         <v>5</v>
       </c>
-      <c r="BC63" t="n">
+      <c r="BB63" t="n">
         <v>0</v>
       </c>
+      <c r="BC63" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE63" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF63" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG63" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -7986,7 +7890,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -8001,7 +7905,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -8058,20 +7962,20 @@
       <c r="BA64" t="n">
         <v>5</v>
       </c>
-      <c r="BC64" t="n">
+      <c r="BB64" t="n">
         <v>0</v>
       </c>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE64" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF64" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG64" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -8101,7 +8005,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -8116,7 +8020,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -8173,20 +8077,20 @@
       <c r="BA65" t="n">
         <v>5</v>
       </c>
-      <c r="BC65" t="n">
+      <c r="BB65" t="n">
         <v>0</v>
       </c>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE65" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF65" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG65" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -8216,7 +8120,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -8231,7 +8135,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -8288,20 +8192,20 @@
       <c r="BA66" t="n">
         <v>5</v>
       </c>
-      <c r="BC66" t="n">
+      <c r="BB66" t="n">
         <v>0</v>
       </c>
+      <c r="BC66" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE66" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF66" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG66" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -8331,7 +8235,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -8346,7 +8250,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -8403,20 +8307,20 @@
       <c r="BA67" t="n">
         <v>5</v>
       </c>
-      <c r="BC67" t="n">
+      <c r="BB67" t="n">
         <v>0</v>
       </c>
+      <c r="BC67" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE67" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF67" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG67" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -8446,7 +8350,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G68" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -8461,7 +8365,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -8518,20 +8422,20 @@
       <c r="BA68" t="n">
         <v>5</v>
       </c>
-      <c r="BC68" t="n">
+      <c r="BB68" t="n">
         <v>0</v>
       </c>
+      <c r="BC68" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE68" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF68" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG68" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -8561,7 +8465,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G69" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -8576,7 +8480,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -8633,20 +8537,20 @@
       <c r="BA69" t="n">
         <v>5</v>
       </c>
-      <c r="BC69" t="n">
+      <c r="BB69" t="n">
         <v>0</v>
       </c>
+      <c r="BC69" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE69" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF69" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG69" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -8676,7 +8580,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G70" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -8691,7 +8595,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -8748,20 +8652,20 @@
       <c r="BA70" t="n">
         <v>5</v>
       </c>
-      <c r="BC70" t="n">
+      <c r="BB70" t="n">
         <v>0</v>
       </c>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE70" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF70" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG70" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -8791,7 +8695,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G71" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -8806,7 +8710,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -8863,20 +8767,20 @@
       <c r="BA71" t="n">
         <v>5</v>
       </c>
-      <c r="BC71" t="n">
+      <c r="BB71" t="n">
         <v>0</v>
       </c>
+      <c r="BC71" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE71" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF71" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG71" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -8906,7 +8810,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G72" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -8921,7 +8825,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -8978,20 +8882,20 @@
       <c r="BA72" t="n">
         <v>5</v>
       </c>
-      <c r="BC72" t="n">
+      <c r="BB72" t="n">
         <v>0</v>
       </c>
+      <c r="BC72" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE72" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF72" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG72" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -9021,7 +8925,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G73" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -9036,7 +8940,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -9093,20 +8997,20 @@
       <c r="BA73" t="n">
         <v>5</v>
       </c>
-      <c r="BC73" t="n">
+      <c r="BB73" t="n">
         <v>0</v>
       </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE73" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF73" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG73" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -9136,7 +9040,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G74" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -9151,7 +9055,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -9208,20 +9112,20 @@
       <c r="BA74" t="n">
         <v>5</v>
       </c>
-      <c r="BC74" t="n">
+      <c r="BB74" t="n">
         <v>0</v>
       </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE74" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF74" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG74" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -9251,7 +9155,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G75" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -9266,7 +9170,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -9323,20 +9227,20 @@
       <c r="BA75" t="n">
         <v>5</v>
       </c>
-      <c r="BC75" t="n">
+      <c r="BB75" t="n">
         <v>0</v>
       </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE75" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF75" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG75" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -9366,7 +9270,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G76" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -9381,7 +9285,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -9438,20 +9342,20 @@
       <c r="BA76" t="n">
         <v>5</v>
       </c>
-      <c r="BC76" t="n">
+      <c r="BB76" t="n">
         <v>0</v>
       </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE76" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF76" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG76" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -9481,7 +9385,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G77" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -9496,7 +9400,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -9553,20 +9457,20 @@
       <c r="BA77" t="n">
         <v>5</v>
       </c>
-      <c r="BC77" t="n">
+      <c r="BB77" t="n">
         <v>0</v>
       </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE77" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF77" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG77" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -9596,7 +9500,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G78" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -9611,7 +9515,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -9668,20 +9572,20 @@
       <c r="BA78" t="n">
         <v>5</v>
       </c>
-      <c r="BC78" t="n">
+      <c r="BB78" t="n">
         <v>0</v>
       </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE78" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF78" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG78" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -9711,7 +9615,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G79" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -9726,7 +9630,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -9783,20 +9687,20 @@
       <c r="BA79" t="n">
         <v>5</v>
       </c>
-      <c r="BC79" t="n">
+      <c r="BB79" t="n">
         <v>0</v>
       </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE79" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF79" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG79" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -9826,7 +9730,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G80" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -9841,7 +9745,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -9898,20 +9802,20 @@
       <c r="BA80" t="n">
         <v>5</v>
       </c>
-      <c r="BC80" t="n">
+      <c r="BB80" t="n">
         <v>0</v>
       </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE80" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF80" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG80" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -9941,7 +9845,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G81" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -9956,7 +9860,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -10013,20 +9917,20 @@
       <c r="BA81" t="n">
         <v>5</v>
       </c>
-      <c r="BC81" t="n">
+      <c r="BB81" t="n">
         <v>0</v>
       </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE81" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF81" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG81" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -10056,7 +9960,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G82" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -10071,7 +9975,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -10128,20 +10032,20 @@
       <c r="BA82" t="n">
         <v>5</v>
       </c>
-      <c r="BC82" t="n">
+      <c r="BB82" t="n">
         <v>0</v>
       </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE82" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF82" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG82" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -10171,7 +10075,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G83" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -10186,7 +10090,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -10243,20 +10147,20 @@
       <c r="BA83" t="n">
         <v>5</v>
       </c>
-      <c r="BC83" t="n">
+      <c r="BB83" t="n">
         <v>0</v>
       </c>
+      <c r="BC83" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE83" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF83" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG83" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -10286,7 +10190,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G84" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -10301,7 +10205,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -10358,20 +10262,20 @@
       <c r="BA84" t="n">
         <v>5</v>
       </c>
-      <c r="BC84" t="n">
+      <c r="BB84" t="n">
         <v>0</v>
       </c>
+      <c r="BC84" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE84" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF84" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG84" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -10401,7 +10305,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G85" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -10416,7 +10320,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -10473,20 +10377,20 @@
       <c r="BA85" t="n">
         <v>5</v>
       </c>
-      <c r="BC85" t="n">
+      <c r="BB85" t="n">
         <v>0</v>
       </c>
+      <c r="BC85" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE85" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF85" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG85" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -10516,7 +10420,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G86" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -10531,7 +10435,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -10588,20 +10492,20 @@
       <c r="BA86" t="n">
         <v>5</v>
       </c>
-      <c r="BC86" t="n">
+      <c r="BB86" t="n">
         <v>0</v>
       </c>
+      <c r="BC86" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE86" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF86" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG86" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -10631,7 +10535,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G87" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -10646,7 +10550,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -10703,20 +10607,20 @@
       <c r="BA87" t="n">
         <v>5</v>
       </c>
-      <c r="BC87" t="n">
+      <c r="BB87" t="n">
         <v>0</v>
       </c>
+      <c r="BC87" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE87" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF87" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG87" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -10746,7 +10650,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G88" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -10761,7 +10665,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -10818,20 +10722,20 @@
       <c r="BA88" t="n">
         <v>5</v>
       </c>
-      <c r="BC88" t="n">
+      <c r="BB88" t="n">
         <v>0</v>
       </c>
+      <c r="BC88" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
+        </is>
+      </c>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
+        </is>
+      </c>
       <c r="BE88" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/montego-bay-project</t>
-        </is>
-      </c>
-      <c r="BF88" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/chec-to-carry-out-montego-bay-perimeter-road-project/</t>
-        </is>
-      </c>
-      <c r="BG88" t="inlineStr">
         <is>
           <t>https://en.ccccltd.cn/xwzx/ztbd/202112/t20211208_145207.html</t>
         </is>
@@ -10861,7 +10765,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G89" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -10876,7 +10780,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -10933,20 +10837,20 @@
       <c r="BA89" t="n">
         <v>5</v>
       </c>
-      <c r="BC89" t="n">
+      <c r="BB89" t="n">
         <v>0</v>
       </c>
+      <c r="BC89" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE89" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF89" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG89" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -10976,7 +10880,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G90" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -10991,7 +10895,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -11048,20 +10952,20 @@
       <c r="BA90" t="n">
         <v>5</v>
       </c>
-      <c r="BC90" t="n">
+      <c r="BB90" t="n">
         <v>0</v>
       </c>
+      <c r="BC90" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE90" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF90" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG90" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -11091,7 +10995,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G91" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -11106,7 +11010,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -11163,20 +11067,20 @@
       <c r="BA91" t="n">
         <v>5</v>
       </c>
-      <c r="BC91" t="n">
+      <c r="BB91" t="n">
         <v>0</v>
       </c>
+      <c r="BC91" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE91" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF91" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG91" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -11206,7 +11110,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="G92" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -11221,7 +11125,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -11278,20 +11182,20 @@
       <c r="BA92" t="n">
         <v>5</v>
       </c>
-      <c r="BC92" t="n">
+      <c r="BB92" t="n">
         <v>0</v>
       </c>
+      <c r="BC92" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE92" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF92" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG92" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -11321,7 +11225,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G93" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -11336,7 +11240,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -11393,20 +11297,20 @@
       <c r="BA93" t="n">
         <v>5</v>
       </c>
-      <c r="BC93" t="n">
+      <c r="BB93" t="n">
         <v>0</v>
       </c>
+      <c r="BC93" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE93" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF93" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG93" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -11436,7 +11340,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G94" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -11451,7 +11355,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -11508,20 +11412,20 @@
       <c r="BA94" t="n">
         <v>5</v>
       </c>
-      <c r="BC94" t="n">
+      <c r="BB94" t="n">
         <v>0</v>
       </c>
+      <c r="BC94" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE94" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF94" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG94" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -11551,7 +11455,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="G95" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -11566,7 +11470,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -11623,20 +11527,20 @@
       <c r="BA95" t="n">
         <v>5</v>
       </c>
-      <c r="BC95" t="n">
+      <c r="BB95" t="n">
         <v>0</v>
       </c>
+      <c r="BC95" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE95" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF95" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG95" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -11666,7 +11570,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="G96" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -11681,7 +11585,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -11738,20 +11642,20 @@
       <c r="BA96" t="n">
         <v>5</v>
       </c>
-      <c r="BC96" t="n">
+      <c r="BB96" t="n">
         <v>0</v>
       </c>
+      <c r="BC96" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE96" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF96" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG96" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -11781,7 +11685,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G97" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -11796,7 +11700,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -11853,20 +11757,20 @@
       <c r="BA97" t="n">
         <v>5</v>
       </c>
-      <c r="BC97" t="n">
+      <c r="BB97" t="n">
         <v>0</v>
       </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE97" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF97" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG97" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -11896,7 +11800,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G98" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -11911,7 +11815,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -11968,20 +11872,20 @@
       <c r="BA98" t="n">
         <v>5</v>
       </c>
-      <c r="BC98" t="n">
+      <c r="BB98" t="n">
         <v>0</v>
       </c>
+      <c r="BC98" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE98" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF98" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG98" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -12011,7 +11915,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G99" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -12026,7 +11930,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -12083,20 +11987,20 @@
       <c r="BA99" t="n">
         <v>5</v>
       </c>
-      <c r="BC99" t="n">
+      <c r="BB99" t="n">
         <v>0</v>
       </c>
+      <c r="BC99" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE99" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF99" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG99" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -12126,7 +12030,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G100" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -12141,7 +12045,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -12198,20 +12102,20 @@
       <c r="BA100" t="n">
         <v>5</v>
       </c>
-      <c r="BC100" t="n">
+      <c r="BB100" t="n">
         <v>0</v>
       </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE100" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF100" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG100" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -12241,7 +12145,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G101" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -12256,7 +12160,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -12313,20 +12217,20 @@
       <c r="BA101" t="n">
         <v>5</v>
       </c>
-      <c r="BC101" t="n">
+      <c r="BB101" t="n">
         <v>0</v>
       </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE101" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF101" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG101" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -12356,7 +12260,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G102" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -12371,7 +12275,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -12428,20 +12332,20 @@
       <c r="BA102" t="n">
         <v>5</v>
       </c>
-      <c r="BC102" t="n">
+      <c r="BB102" t="n">
         <v>0</v>
       </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE102" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF102" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG102" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -12471,7 +12375,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G103" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -12486,7 +12390,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -12543,20 +12447,20 @@
       <c r="BA103" t="n">
         <v>5</v>
       </c>
-      <c r="BC103" t="n">
+      <c r="BB103" t="n">
         <v>0</v>
       </c>
+      <c r="BC103" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE103" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF103" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG103" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -12586,7 +12490,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G104" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -12601,7 +12505,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -12658,20 +12562,20 @@
       <c r="BA104" t="n">
         <v>5</v>
       </c>
-      <c r="BC104" t="n">
+      <c r="BB104" t="n">
         <v>0</v>
       </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE104" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF104" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG104" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -12701,7 +12605,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="G105" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -12716,7 +12620,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -12773,20 +12677,20 @@
       <c r="BA105" t="n">
         <v>5</v>
       </c>
-      <c r="BC105" t="n">
+      <c r="BB105" t="n">
         <v>0</v>
       </c>
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE105" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF105" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG105" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -12816,7 +12720,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="G106" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -12831,7 +12735,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -12888,20 +12792,20 @@
       <c r="BA106" t="n">
         <v>5</v>
       </c>
-      <c r="BC106" t="n">
+      <c r="BB106" t="n">
         <v>0</v>
       </c>
+      <c r="BC106" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE106" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF106" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG106" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -12931,7 +12835,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="G107" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -12946,7 +12850,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -13003,20 +12907,20 @@
       <c r="BA107" t="n">
         <v>5</v>
       </c>
-      <c r="BC107" t="n">
+      <c r="BB107" t="n">
         <v>0</v>
       </c>
+      <c r="BC107" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE107" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF107" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG107" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -13046,7 +12950,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="G108" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -13061,7 +12965,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -13118,20 +13022,20 @@
       <c r="BA108" t="n">
         <v>5</v>
       </c>
-      <c r="BC108" t="n">
+      <c r="BB108" t="n">
         <v>0</v>
       </c>
+      <c r="BC108" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE108" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF108" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG108" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -13161,7 +13065,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="G109" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -13176,7 +13080,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -13233,20 +13137,20 @@
       <c r="BA109" t="n">
         <v>5</v>
       </c>
-      <c r="BC109" t="n">
+      <c r="BB109" t="n">
         <v>0</v>
       </c>
+      <c r="BC109" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE109" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF109" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG109" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -13276,7 +13180,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="G110" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -13291,7 +13195,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -13348,20 +13252,20 @@
       <c r="BA110" t="n">
         <v>5</v>
       </c>
-      <c r="BC110" t="n">
+      <c r="BB110" t="n">
         <v>0</v>
       </c>
+      <c r="BC110" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE110" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF110" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG110" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -13391,7 +13295,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="G111" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -13406,7 +13310,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -13463,20 +13367,20 @@
       <c r="BA111" t="n">
         <v>5</v>
       </c>
-      <c r="BC111" t="n">
+      <c r="BB111" t="n">
         <v>0</v>
       </c>
+      <c r="BC111" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE111" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF111" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG111" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -13506,7 +13410,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="G112" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -13521,7 +13425,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -13578,20 +13482,20 @@
       <c r="BA112" t="n">
         <v>5</v>
       </c>
-      <c r="BC112" t="n">
+      <c r="BB112" t="n">
         <v>0</v>
       </c>
+      <c r="BC112" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE112" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF112" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG112" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -13621,7 +13525,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="G113" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -13636,7 +13540,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -13693,20 +13597,20 @@
       <c r="BA113" t="n">
         <v>5</v>
       </c>
-      <c r="BC113" t="n">
+      <c r="BB113" t="n">
         <v>0</v>
       </c>
+      <c r="BC113" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE113" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF113" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG113" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -13736,7 +13640,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="G114" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -13751,7 +13655,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -13808,20 +13712,20 @@
       <c r="BA114" t="n">
         <v>5</v>
       </c>
-      <c r="BC114" t="n">
+      <c r="BB114" t="n">
         <v>0</v>
       </c>
+      <c r="BC114" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE114" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF114" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG114" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -13851,7 +13755,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="G115" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -13866,7 +13770,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -13923,20 +13827,20 @@
       <c r="BA115" t="n">
         <v>5</v>
       </c>
-      <c r="BC115" t="n">
+      <c r="BB115" t="n">
         <v>0</v>
       </c>
+      <c r="BC115" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE115" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF115" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG115" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -13966,7 +13870,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="G116" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -13981,7 +13885,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -14038,20 +13942,20 @@
       <c r="BA116" t="n">
         <v>5</v>
       </c>
-      <c r="BC116" t="n">
+      <c r="BB116" t="n">
         <v>0</v>
       </c>
+      <c r="BC116" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE116" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF116" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG116" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -14081,7 +13985,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="G117" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -14096,7 +14000,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -14153,20 +14057,20 @@
       <c r="BA117" t="n">
         <v>5</v>
       </c>
-      <c r="BC117" t="n">
+      <c r="BB117" t="n">
         <v>0</v>
       </c>
+      <c r="BC117" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE117" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF117" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG117" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -14196,7 +14100,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="G118" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -14211,7 +14115,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -14268,20 +14172,20 @@
       <c r="BA118" t="n">
         <v>5</v>
       </c>
-      <c r="BC118" t="n">
+      <c r="BB118" t="n">
         <v>0</v>
       </c>
+      <c r="BC118" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE118" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF118" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG118" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -14311,7 +14215,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="G119" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -14326,7 +14230,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -14383,20 +14287,20 @@
       <c r="BA119" t="n">
         <v>5</v>
       </c>
-      <c r="BC119" t="n">
+      <c r="BB119" t="n">
         <v>0</v>
       </c>
+      <c r="BC119" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE119" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF119" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG119" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -14426,7 +14330,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="G120" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -14441,7 +14345,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -14498,20 +14402,20 @@
       <c r="BA120" t="n">
         <v>5</v>
       </c>
-      <c r="BC120" t="n">
+      <c r="BB120" t="n">
         <v>0</v>
       </c>
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE120" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF120" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG120" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -14541,7 +14445,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="G121" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -14556,7 +14460,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -14613,20 +14517,20 @@
       <c r="BA121" t="n">
         <v>5</v>
       </c>
-      <c r="BC121" t="n">
+      <c r="BB121" t="n">
         <v>0</v>
       </c>
+      <c r="BC121" t="inlineStr">
+        <is>
+          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
+        </is>
+      </c>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
+        </is>
+      </c>
       <c r="BE121" t="inlineStr">
-        <is>
-          <t>https://h2kjamaica.com.jm/projects/may-pen-to-williamsfield-highway</t>
-        </is>
-      </c>
-      <c r="BF121" t="inlineStr">
-        <is>
-          <t>https://jis.gov.jm/prime-minister-holness-opens-may-pen-to-williamsfield-leg-of-southern-coastal-highway/</t>
-        </is>
-      </c>
-      <c r="BG121" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/may-pen-to-williamsfield-highway-on-track-for-august-completion/</t>
         </is>
@@ -14656,7 +14560,7 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="G122" s="1" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -14671,12 +14575,12 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC)</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="L122" t="n">
@@ -14725,20 +14629,15 @@
       <c r="BA122" t="n">
         <v>3</v>
       </c>
-      <c r="BC122" t="n">
-        <v>1</v>
+      <c r="BB122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>https://megid.gov.jm/north-coast-traffic-relief-coming-goj-signs-mou-with-chec-for-north-south-highway-extension-project-nshep-feasibility-studies/</t>
+        </is>
       </c>
       <c r="BD122" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE122" t="inlineStr">
-        <is>
-          <t>https://megid.gov.jm/north-coast-traffic-relief-coming-goj-signs-mou-with-chec-for-north-south-highway-extension-project-nshep-feasibility-studies/</t>
-        </is>
-      </c>
-      <c r="BF122" t="inlineStr">
         <is>
           <t>https://jis.gov.jm/feasibility-studies-to-be-conducted-for-north-south-highway-expansion/</t>
         </is>

--- a/data/sources/countries/jamaica.xlsx
+++ b/data/sources/countries/jamaica.xlsx
@@ -9159,12 +9159,12 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Arrendamiento y compra de los ingenios azucareros de Frome, Monymusk y Bernard Lodge junto con el control de las tierras canaveras circundantes</t>
+          <t>Arrendamiento y compra de los ingenios azucareros de Frome, Monymusk y Bernard Lodge junto con el control de las.</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lease and purchase of the Frome, Monymusk and Bernard Lodge sugar estates together with control of the surrounding cane lands</t>
+          <t>Lease and purchase of the Frome, Monymusk and Bernard Lodge sugar estates together with control of the surrounding cane.</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -9312,12 +9312,12 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Arrendamiento y compra de los ingenios azucareros de Frome, Monymusk y Bernard Lodge junto con el control de las tierras canaveras circundantes</t>
+          <t>Arrendamiento y compra de los ingenios azucareros de Frome, Monymusk y Bernard Lodge junto con el control de las.</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lease and purchase of the Frome, Monymusk and Bernard Lodge sugar estates together with control of the surrounding cane lands</t>
+          <t>Lease and purchase of the Frome, Monymusk and Bernard Lodge sugar estates together with control of the surrounding cane.</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Arrendamiento y compra de los ingenios azucareros de Frome, Monymusk y Bernard Lodge junto con el control de las tierras canaveras circundantes</t>
+          <t>Arrendamiento y compra de los ingenios azucareros de Frome, Monymusk y Bernard Lodge junto con el control de las.</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lease and purchase of the Frome, Monymusk and Bernard Lodge sugar estates together with control of the surrounding cane lands</t>
+          <t>Lease and purchase of the Frome, Monymusk and Bernard Lodge sugar estates together with control of the surrounding cane.</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -18443,7 +18443,7 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Develop the feasibility studies for the North-South Highway Extension Project (NSHEP), covering technical, financial, economic, environmental and social aspects. CHEC will carry out the studies at no cost to the Government of Jamaica.</t>
+          <t>Develop the feasibility studies for the North-South Highway Extension Project (NSHEP), covering technical, financial,</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
